--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0026.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0026.xlsx
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Lần đầu tiên cảm nhận được những cảm xúc này, ta không biết phải làm gì...</t>
+          <t>Lần đầu tiên cảm nhận được những cảm xúc này, tao không biết phải làm gì...</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ta chẳng cảm thấy gì cả...</t>
+          <t>Tao chẳng cảm thấy gì cả...</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Ta biết ngươi còn có hành trình riêng phải hoàn thành.</t>
+          <t>Tao biết mày còn có hành trình riêng phải hoàn thành.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Ôi, chuyện này có liên quan gì đến ta chứ?!</t>
+          <t>Ôi, chuyện này có liên quan gì đến tao chứ?!</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Bộ Điều Tần Tinh Tú, Rover {Male=anh;Female=cô}. Chúng ta đã chờ đợi khoảnh khắc này từ rất lâu rồi.</t>
+          <t>Bộ Điều Tần Tinh Tú, Vận Mệnh Giả {Male=himself;Female=herself}. Chúng ta đã chờ đợi khoảnh khắc này từ rất lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Vấn đề này vượt quá khả năng của chúng ta. Hơn nữa, họ còn nhắc đến Rover và sự sụp đổ của Thành Phố Cảng Guixu.</t>
+          <t>Vấn đề này vượt quá khả năng của chúng ta. Hơn nữa, họ còn nhắc đến Vận Mệnh Giả và sự sụp đổ của Thành Phố Cảng Guixu.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Chính cậu đã kể cho ta nghe về sự thăng trầm của nó.</t>
+          <t>Chính cậu đã kể cho tao nghe về sự thăng trầm của nó.</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Ta nhớ nụ cười của ngươi khi kể về sự phồn vinh của nơi đó.</t>
+          <t>Tao nhớ nụ cười của mày khi kể về sự phồn vinh của nơi đó.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Thật là một kẻ nghiện việc... Được rồi, lần này ta sẽ chở ngươi về.</t>
+          <t>Thật là một kẻ nghiện việc... Được rồi, lần này tao sẽ chở mày về.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Nếu biết cậu thích, thì việc gì ta cũng sẵn lòng.</t>
+          <t>Nếu biết cậu thích, thì việc gì tao cũng sẵn lòng.</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Xin chào! Có chuyện gì mà cậu lại đến đây thế?</t>
+          <t>Xin chào! Có chuyện gì mà bạn lại đến đây thế?</t>
         </is>
       </c>
     </row>
